--- a/output/pdf_financials_xlsx/SMRV.xlsx
+++ b/output/pdf_financials_xlsx/SMRV.xlsx
@@ -5033,46 +5033,46 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>3.610287</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>4.013129</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>4.289158</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>4.289158</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>4.289158</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>4.289158</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>4.289158</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>4.289158</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>4.592693</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>4.723052</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>4.845529</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>4.937702</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>4.937702</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>4.937702</v>
       </c>
     </row>
     <row r="93">
@@ -8286,7 +8286,11 @@
           <t>Reserve 5</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -8782,7 +8786,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -9834,7 +9842,11 @@
           <t>Share based payment reserve 5</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -10400,7 +10412,11 @@
           <t>Share based payment reserve 4</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -10812,7 +10828,11 @@
           <t>Share based payment reserve 4</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -11592,7 +11612,11 @@
           <t>Share based payment reserve 6</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" s="5" t="n">
         <v>3.610287</v>
       </c>
@@ -12114,7 +12138,11 @@
           <t>Share based payment reserve 6</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SMRV.xlsx
+++ b/output/pdf_financials_xlsx/SMRV.xlsx
@@ -948,10 +948,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.019426</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.003591</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.872873</v>
+        <v>-1.892299</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.493081</v>
+        <v>-0.496672</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-0.215782</v>
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.872873</v>
+        <v>-1.892299</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.493081</v>
+        <v>-0.496672</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-0.215782</v>
@@ -2119,46 +2119,46 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.558623</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.336284</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.213177</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.06683799999999999</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.207566</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.078781</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.31123</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.115104</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.197352</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.595542</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.661705</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.458372</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.343185</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.156131</v>
       </c>
     </row>
     <row r="35">
@@ -2217,46 +2217,46 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.558623</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.336284</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.213177</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.06683799999999999</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.207566</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.078781</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.31123</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.115104</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.197352</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.595542</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.661705</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.458372</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.343185</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.156131</v>
       </c>
     </row>
     <row r="37">
@@ -2805,46 +2805,46 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.558623</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.339399</v>
+        <v>0.003115</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.223439</v>
+        <v>0.010262</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.06683799999999999</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.207566</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.078781</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.31123</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.115104</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.213974</v>
+        <v>0.016622</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.627324</v>
+        <v>0.031782</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.7008</v>
+        <v>0.039095</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.490433</v>
+        <v>0.032061</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.359644</v>
+        <v>0.016459</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.174232</v>
+        <v>0.018101</v>
       </c>
     </row>
     <row r="49">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9048,7 +9048,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
@@ -27254,7 +27254,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -28548,7 +28548,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">

--- a/output/pdf_financials_xlsx/SMRV.xlsx
+++ b/output/pdf_financials_xlsx/SMRV.xlsx
@@ -6407,10 +6407,10 @@
         <v>0</v>
       </c>
       <c r="J120" s="3" t="n">
-        <v>0</v>
+        <v>0.9567099999999999</v>
       </c>
       <c r="K120" s="3" t="n">
-        <v>0</v>
+        <v>0.296714</v>
       </c>
       <c r="L120" s="3" t="n">
         <v>0</v>
@@ -14932,7 +14932,11 @@
           <t>Issuance of common shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -16266,7 +16270,11 @@
           <t>Issuance of common shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SMRV.xlsx
+++ b/output/pdf_financials_xlsx/SMRV.xlsx
@@ -1140,10 +1140,8 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>2.739283</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-1.872873</v>
@@ -1394,10 +1392,8 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>2.739283</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-1.872873</v>
@@ -1543,10 +1539,8 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>2.739283</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-1.872873</v>
@@ -1692,10 +1686,8 @@
           <t>Shares Outstanding (Diluted Average)</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="3" t="n">
+        <v>5.828262</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>20.8097</v>
@@ -1755,10 +1747,8 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>2.739283</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-1.892299</v>
@@ -1855,10 +1845,8 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>2.739283</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-1.892299</v>
@@ -1983,10 +1971,8 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -3621,31 +3607,31 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.06591</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.034586</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.026771</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.003057</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.048276</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.011189</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.030546</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.000402</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.000624</v>
       </c>
       <c r="K64" s="3" t="n">
         <v>0</v>
@@ -3768,46 +3754,46 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.048742</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.04658</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.049493</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.048556</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.048056</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.048069</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.0266</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.07675</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.1305</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.193</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.1978</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.200951</v>
       </c>
     </row>
     <row r="68">
@@ -5347,10 +5333,8 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>2.739283</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-1.872873</v>
@@ -5457,22 +5441,22 @@
         <v>0</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>0.01022</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002334</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002305</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001615</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>0.003004</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0</v>
+        <v>-0.017587</v>
       </c>
       <c r="K101" s="3" t="n">
         <v>0</v>
@@ -5484,10 +5468,10 @@
         <v>0</v>
       </c>
       <c r="N101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000423</v>
       </c>
       <c r="O101" s="3" t="n">
-        <v>0</v>
+        <v>-0.003068</v>
       </c>
     </row>
     <row r="102">
@@ -5702,22 +5686,22 @@
         <v>-0.03328</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.007779</v>
+        <v>0.017999</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.08033800000000001</v>
+        <v>0.078004</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>-0.037587</v>
+        <v>-0.039892</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.01937</v>
+        <v>0.017755</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>-0.030157</v>
+        <v>-0.027153</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0.014822</v>
+        <v>-0.002765</v>
       </c>
       <c r="K106" s="3" t="n">
         <v>0.077778</v>
@@ -5729,10 +5713,10 @@
         <v>0.061955</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0.005861</v>
+        <v>0.005438</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0.015567</v>
+        <v>0.012499</v>
       </c>
     </row>
     <row r="107">
@@ -12824,7 +12808,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -15880,7 +15868,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -19328,7 +19320,11 @@
           <t>Issuance of common shares for private placement 6 14,358,000 406,943 247,355</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -20790,7 +20786,11 @@
           <t>Net Income (loss)</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E161" s="5" t="n">
         <v>2.739283</v>
       </c>
